--- a/src_files/data_files/balticData.xlsx
+++ b/src_files/data_files/balticData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9489953-CCD9-473F-AA9B-2CB06E500400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521D4967-92A0-46D8-8CD7-420032C70BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src_files/data_files/balticData.xlsx
+++ b/src_files/data_files/balticData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521D4967-92A0-46D8-8CD7-420032C70BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EE5302-6D43-4684-8AE5-EA4D94C7114E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18120" yWindow="-105" windowWidth="18240" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unitdata_Baltic" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="111">
   <si>
     <t>Country</t>
   </si>
@@ -369,9 +369,6 @@
   </si>
   <si>
     <t>method</t>
-  </si>
-  <si>
-    <t>remove</t>
   </si>
   <si>
     <t>Generator_ID</t>
@@ -443,7 +440,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,6 +468,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,7 +635,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -720,6 +723,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1023,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>8</v>
@@ -1092,6 +1096,10 @@
         <f ca="1">H2/J2</f>
         <v>0.14992834307132621</v>
       </c>
+      <c r="N2" s="35" t="str">
+        <f ca="1">IF(H2&lt;10, "remove", "")</f>
+        <v/>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
@@ -1123,6 +1131,10 @@
         <f t="shared" ref="L3:L4" ca="1" si="0">H3/J3</f>
         <v>1.1228452358401211</v>
       </c>
+      <c r="N3" s="35" t="str">
+        <f t="shared" ref="N3:N30" ca="1" si="1">IF(H3&lt;10, "remove", "")</f>
+        <v/>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -1154,6 +1166,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>0.25</v>
       </c>
+      <c r="N4" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>remove</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
@@ -1182,6 +1198,10 @@
       </c>
       <c r="K5" s="31"/>
       <c r="L5" s="31"/>
+      <c r="N5" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
@@ -1210,6 +1230,10 @@
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
+      <c r="N6" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
@@ -1238,6 +1262,10 @@
       </c>
       <c r="K7" s="31"/>
       <c r="L7" s="31"/>
+      <c r="N7" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>remove</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
@@ -1265,6 +1293,10 @@
       </c>
       <c r="K8" s="31"/>
       <c r="L8" s="31"/>
+      <c r="N8" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
@@ -1292,6 +1324,10 @@
       </c>
       <c r="K9" s="31"/>
       <c r="L9" s="31"/>
+      <c r="N9" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
@@ -1323,6 +1359,10 @@
         <f ca="1">H10/J10</f>
         <v>0.27127098966218161</v>
       </c>
+      <c r="N10" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
@@ -1351,8 +1391,12 @@
       </c>
       <c r="K11" s="31"/>
       <c r="L11" s="31">
-        <f t="shared" ref="L11:L12" ca="1" si="1">H11/J11</f>
+        <f t="shared" ref="L11:L12" ca="1" si="2">H11/J11</f>
         <v>0.64984483088094791</v>
+      </c>
+      <c r="N11" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1382,8 +1426,12 @@
       </c>
       <c r="K12" s="31"/>
       <c r="L12" s="31">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.33653736102685788</v>
+      </c>
+      <c r="N12" s="35" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33653736102685788</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1413,6 +1461,10 @@
       </c>
       <c r="K13" s="31"/>
       <c r="L13" s="31"/>
+      <c r="N13" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
@@ -1441,6 +1493,10 @@
       </c>
       <c r="K14" s="31"/>
       <c r="L14" s="31"/>
+      <c r="N14" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
@@ -1469,6 +1525,10 @@
       </c>
       <c r="K15" s="31"/>
       <c r="L15" s="31"/>
+      <c r="N15" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
@@ -1496,6 +1556,10 @@
       </c>
       <c r="K16" s="31"/>
       <c r="L16" s="31"/>
+      <c r="N16" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
@@ -1523,6 +1587,10 @@
       </c>
       <c r="K17" s="31"/>
       <c r="L17" s="31"/>
+      <c r="N17" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
@@ -1554,6 +1622,10 @@
         <f ca="1">H18/J18</f>
         <v>0.31785268414481899</v>
       </c>
+      <c r="N18" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
@@ -1582,8 +1654,12 @@
       </c>
       <c r="K19" s="31"/>
       <c r="L19" s="31">
-        <f t="shared" ref="L19" ca="1" si="2">H19/J19</f>
+        <f t="shared" ref="L19" ca="1" si="3">H19/J19</f>
         <v>0.28431372549019607</v>
+      </c>
+      <c r="N19" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1619,6 +1695,10 @@
       <c r="M20" t="s">
         <v>107</v>
       </c>
+      <c r="N20" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
@@ -1650,6 +1730,10 @@
         <f ca="1">H21/J21</f>
         <v>0.24125000000000002</v>
       </c>
+      <c r="N21" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
@@ -1678,6 +1762,10 @@
       </c>
       <c r="K22" s="31"/>
       <c r="L22" s="31"/>
+      <c r="N22" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
@@ -1706,6 +1794,10 @@
       </c>
       <c r="K23" s="31"/>
       <c r="L23" s="31"/>
+      <c r="N23" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
@@ -1734,6 +1826,10 @@
       </c>
       <c r="K24" s="31"/>
       <c r="L24" s="31"/>
+      <c r="N24" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
@@ -1762,6 +1858,10 @@
       </c>
       <c r="K25" s="31"/>
       <c r="L25" s="31"/>
+      <c r="N25" s="35" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
@@ -1789,6 +1889,10 @@
       </c>
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
+      <c r="N26" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
@@ -1816,6 +1920,10 @@
       </c>
       <c r="K27" s="31"/>
       <c r="L27" s="31"/>
+      <c r="N27" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1830,8 +1938,9 @@
       <c r="E28" s="32">
         <v>1</v>
       </c>
-      <c r="N28" t="s">
-        <v>110</v>
+      <c r="N28" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>remove</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -1847,8 +1956,9 @@
       <c r="E29" s="32">
         <v>1</v>
       </c>
-      <c r="N29" t="s">
-        <v>110</v>
+      <c r="N29" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>remove</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -1864,8 +1974,9 @@
       <c r="E30" s="32">
         <v>1</v>
       </c>
-      <c r="N30" t="s">
-        <v>110</v>
+      <c r="N30" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v>remove</v>
       </c>
     </row>
   </sheetData>
